--- a/Results/GWP 20a/carbon dioxide climate change GWP 20a results.xlsx
+++ b/Results/GWP 20a/carbon dioxide climate change GWP 20a results.xlsx
@@ -2074,7 +2074,7 @@
         <v>-0.9735936011319136</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.182420250346334</v>
+        <v>-1.182420250346335</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8379635636245383</v>
@@ -5014,13 +5014,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5169586368923987</v>
+        <v>-0.5169586368924023</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7095382557824912</v>
+        <v>-0.7095382557824913</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2666158190201386</v>
+        <v>-0.2666158190201429</v>
       </c>
       <c r="E2" t="n">
         <v>-0.7179948600035778</v>
@@ -5029,70 +5029,70 @@
         <v>-0.6883272036010976</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05584314393679584</v>
+        <v>0.0558431439367928</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3828488588699739</v>
+        <v>-0.3828488588699759</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5954852278364241</v>
+        <v>-0.5954852278364275</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2485762077121434</v>
+        <v>-0.2485762077121494</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.490786308185249</v>
+        <v>-0.4907863081852523</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2204322432566649</v>
+        <v>-0.22043224325667</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04905206965049629</v>
+        <v>-0.04905206965049695</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4815663408492439</v>
+        <v>-0.4815663408492458</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4928459768728184</v>
+        <v>-0.4928459768728195</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3144686106018991</v>
+        <v>-0.3144686106018988</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7231120542694468</v>
+        <v>-0.7231120542694497</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.4826793539768269</v>
+        <v>-0.4826793539768293</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2547165651436415</v>
+        <v>-0.2547165651436434</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5166510498814182</v>
+        <v>-0.516651049881422</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3208680539550052</v>
+        <v>-0.3208680539550096</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.615406984977066</v>
+        <v>-0.6154069849770664</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.09495913217562284</v>
+        <v>-0.09495913217562524</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1680675764759755</v>
+        <v>-0.1680675764759794</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2472904306601382</v>
+        <v>-0.2472904306601389</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.4852510650718155</v>
+        <v>-0.4852510650718193</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.345983440942391</v>
+        <v>-0.3459834409423947</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.02776661528620228</v>
+        <v>-0.02776661528620294</v>
       </c>
     </row>
     <row r="3">
@@ -5102,13 +5102,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9249379102302469</v>
+        <v>-0.9249379102302504</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.912791550412264</v>
+        <v>-0.9127915504122639</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="E3" t="n">
         <v>-0.9212284225484556</v>
@@ -5117,67 +5117,67 @@
         <v>-0.9245461880131922</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9088664224911095</v>
+        <v>-0.9088664224911087</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9126634206092147</v>
+        <v>-0.9126634206092165</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.911695124353908</v>
+        <v>-0.9116951243539079</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9219450941111289</v>
+        <v>-0.921945094111131</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9191094844746007</v>
+        <v>-0.9191094844746011</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.919804560914063</v>
+        <v>-0.9198045609140619</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9275538849772783</v>
+        <v>-0.9275538849772825</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9181333221804667</v>
+        <v>-0.9181333221804686</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9178208830029628</v>
+        <v>-0.9178208830029633</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9116239917255801</v>
+        <v>-0.9116239917255829</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9263338776613618</v>
+        <v>-0.9263338776613645</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.898407983090412</v>
+        <v>-0.8984079830904128</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9251851745068592</v>
+        <v>-0.9251851745068601</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9116266077706368</v>
+        <v>-0.9116266077706358</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.8967717578783477</v>
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05694696315180518</v>
+        <v>0.05694696315179471</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.01398638127777246</v>
+        <v>-0.01398638127778</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1481939805924574</v>
+        <v>0.1481939805924438</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01792601716307885</v>
+        <v>-0.01792601716308142</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.006583812554418184</v>
+        <v>-0.006583812554428323</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2657264860859461</v>
+        <v>0.2657264860859329</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1058284024444543</v>
+        <v>0.1058284024444468</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02832494285849382</v>
+        <v>0.02832494285848135</v>
       </c>
       <c r="J4" t="n">
-        <v>0.140497478915189</v>
+        <v>0.1404974789151754</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0664864696345602</v>
+        <v>0.06648646963455096</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1650273516433238</v>
+        <v>0.1650273516433056</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2274498693819234</v>
+        <v>0.2274498693819061</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06984703946221027</v>
+        <v>0.06984703946220035</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06573574458379101</v>
+        <v>0.06573574458378337</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1307521999767549</v>
+        <v>0.130752199976741</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.01819353670648005</v>
+        <v>-0.01819353670649482</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06944135924686787</v>
+        <v>0.06944135924685436</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1525311189023482</v>
+        <v>0.1525311189023306</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05705907500544019</v>
+        <v>0.05705907500542465</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1284196780206115</v>
+        <v>0.128419678020601</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.07137517423315827</v>
+        <v>-0.07137517423315691</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2107608272526974</v>
+        <v>0.2107608272526852</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1841136577879159</v>
+        <v>0.1841136577879103</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1552378577195122</v>
+        <v>0.1552378577195004</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06850400075130089</v>
+        <v>0.06850400075128549</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1192654143834677</v>
+        <v>0.119265414383454</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2358554985350635</v>
+        <v>0.2358554985350429</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.09175669124535023</v>
+        <v>-0.09175669124535497</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.08806982044963867</v>
+        <v>-0.08806982044964981</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09200226422170593</v>
+        <v>-0.09200226422170472</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.09268285854925597</v>
+        <v>-0.0926828585492797</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.08589882268536203</v>
+        <v>-0.08589882268536844</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1015545120800435</v>
+        <v>-0.1015545120800466</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08697339439129455</v>
+        <v>-0.08697339439130984</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.09066584491333632</v>
+        <v>-0.09066584491335243</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.08963229849823159</v>
+        <v>-0.08963229849824618</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0898856456984188</v>
+        <v>-0.08988564569843321</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.09271018332230677</v>
+        <v>-0.09271018332232245</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08927649880470528</v>
+        <v>-0.08927649880470502</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1816014889403167</v>
+        <v>-0.1816014889403124</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.08690392429030915</v>
+        <v>-0.08690392429032651</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.09226550498170184</v>
+        <v>-0.09226550498171777</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.08208684433300567</v>
+        <v>-0.08208684433301626</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.09184681617062966</v>
+        <v>-0.09184681617065228</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.08690487780801377</v>
+        <v>-0.08690487780802802</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.08088667156620673</v>
+        <v>-0.08088667156620746</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7525076775314978</v>
+        <v>-0.7525076775314993</v>
       </c>
       <c r="C6" t="n">
         <v>-0.8234410219610813</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6612606600908445</v>
+        <v>-0.6612606600908455</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8273806578463747</v>
+        <v>-0.8273806578463746</v>
       </c>
       <c r="F6" t="n">
         <v>-0.8160384532377236</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5807686186279575</v>
+        <v>-0.5807686186279615</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7036262382388455</v>
+        <v>-0.7036262382388471</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7811296978248089</v>
+        <v>-0.781129697824811</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.690811713654375</v>
+        <v>-0.6908117136543768</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7429681710487417</v>
+        <v>-0.7429681710487432</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6444272890399838</v>
+        <v>-0.6444272890399866</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5820047713013837</v>
+        <v>-0.5820047713013839</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7396076012210907</v>
+        <v>-0.7396076012210916</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.780759360130112</v>
+        <v>-0.7807593601301139</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7157429047371486</v>
+        <v>-0.7157429047371504</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8276481773897849</v>
+        <v>-0.8276481773897865</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7400132814364343</v>
+        <v>-0.740013281436436</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6569235217809543</v>
+        <v>-0.6569235217809563</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7523955656778644</v>
+        <v>-0.7523955656778656</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.718075426693299</v>
+        <v>-0.7180754266933008</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8245385459341168</v>
+        <v>-0.8245385459341164</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6357342774612055</v>
+        <v>-0.6357342774612074</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.662381446925988</v>
+        <v>-0.6623814469259899</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.6542167829637903</v>
+        <v>-0.6542167829637924</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7409506399320014</v>
+        <v>-0.7409506399320034</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.6901892262998349</v>
+        <v>-0.6901892262998365</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.5735991421482486</v>
+        <v>-0.5735991421482485</v>
       </c>
     </row>
     <row r="7">
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9012113319286419</v>
+        <v>-0.901211331928644</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8975244611329475</v>
+        <v>-0.8975244611329474</v>
       </c>
       <c r="D7" t="n">
         <v>-0.8963595184913206</v>
@@ -5466,10 +5466,10 @@
         <v>-0.9014569049050024</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.902137499232573</v>
+        <v>-0.9021374992325729</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9323939273992672</v>
+        <v>-0.9323939273992652</v>
       </c>
       <c r="H7" t="n">
         <v>-0.8963595184913206</v>
@@ -5478,7 +5478,7 @@
         <v>-0.8963595184913206</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9328637046495927</v>
+        <v>-0.932863704649596</v>
       </c>
       <c r="K7" t="n">
         <v>-0.8963595184913206</v>
@@ -5490,16 +5490,16 @@
         <v>-0.8964280350746048</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9001204855966439</v>
+        <v>-0.9001204855966478</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9361274032121405</v>
+        <v>-0.9361274032121424</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9363807504123239</v>
+        <v>-0.9363807504123266</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.902164824005611</v>
+        <v>-0.9021648240056104</v>
       </c>
       <c r="R7" t="n">
         <v>-0.8963595184913206</v>
@@ -5511,22 +5511,22 @@
         <v>-0.8963595184913206</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9357716035186076</v>
+        <v>-0.9357716035186071</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9347648606412768</v>
+        <v>-0.934764860641277</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9333990290042185</v>
+        <v>-0.9333990290042186</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9387606096956063</v>
+        <v>-0.9387606096956093</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8915414850163084</v>
+        <v>-0.8915414850163058</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9013014568539423</v>
+        <v>-0.9013014568539457</v>
       </c>
       <c r="AA7" t="n">
         <v>-0.8963595184913206</v>
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8631095776269642</v>
+        <v>-0.8631095776269641</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.8683282481612571</v>
+        <v>-0.868328248161257</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.4772333890085493</v>
+        <v>-0.477233389008551</v>
       </c>
       <c r="C9" t="n">
         <v>-0.682947313873228</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2081892141546907</v>
+        <v>-0.2081892141546889</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6905858814246519</v>
+        <v>-0.6905858814246515</v>
       </c>
       <c r="F9" t="n">
         <v>-0.6595960247262365</v>
       </c>
       <c r="G9" t="n">
-        <v>0.138358397437857</v>
+        <v>0.1383583974378577</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3331052096002285</v>
+        <v>-0.3331052096002286</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5616261510785292</v>
+        <v>-0.561626151078529</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1876877240887923</v>
+        <v>-0.1876877240887932</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4491059090957361</v>
+        <v>-0.4491059090957353</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1585555871998877</v>
+        <v>-0.1585555871998894</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02570083275195038</v>
+        <v>0.02570083275195059</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4391971826334446</v>
+        <v>-0.4391971826334451</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4513194411923582</v>
+        <v>-0.4513194411923571</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2596167523400955</v>
+        <v>-0.2596167523400956</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.6987870830306896</v>
+        <v>-0.6987870830306894</v>
       </c>
       <c r="R9" t="n">
         <v>-0.4403933411693973</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1954010504366784</v>
+        <v>-0.1954010504366777</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4769028243282104</v>
+        <v>-0.4769028243282113</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2664942532450332</v>
+        <v>-0.2664942532450312</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5803005127608319</v>
+        <v>-0.5803005127608309</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.02370925957578422</v>
+        <v>-0.02370925957578521</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1022791232483831</v>
+        <v>-0.1022791232483828</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1874201615042546</v>
+        <v>-0.1874201615042538</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.4431571667722041</v>
+        <v>-0.4431571667722045</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.2934858347315232</v>
+        <v>-0.2934858347315242</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04748168389193775</v>
+        <v>0.04748168389193752</v>
       </c>
     </row>
     <row r="10">
@@ -5721,67 +5721,67 @@
         <v>-0.9156899338600447</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9090015987287411</v>
+        <v>-0.909001598728741</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9134612735323655</v>
+        <v>-0.9134612735323654</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8984178579355117</v>
+        <v>-0.8984178579355115</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="M10" t="n">
         <v>-0.9013842373079278</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.912473545428767</v>
+        <v>-0.9124735454287669</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9094261072743517</v>
+        <v>-0.9094261072743519</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9101731080020125</v>
+        <v>-0.9101731080020123</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9185013297420426</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.908377022738272</v>
+        <v>-0.9083770227382719</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9053056331403286</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9013814258365096</v>
+        <v>-0.9013814258365095</v>
       </c>
       <c r="X10" t="n">
         <v>-0.9171901842319916</v>
@@ -5793,10 +5793,10 @@
         <v>-0.9159556695173999</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.9013842373079508</v>
+        <v>-0.9013842373079507</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.8864407410436271</v>
+        <v>-0.8864407410436269</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1876860721702547</v>
+        <v>-0.1876860721702777</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1734156522262872</v>
+        <v>-0.1734156522263007</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2540754250485947</v>
+        <v>-0.2540754250485983</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.1759807615237828</v>
+        <v>-0.1759807615238076</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01625230872347056</v>
+        <v>0.01625230872346605</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.08486131740555326</v>
+        <v>-0.08486131740556735</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1484943634422276</v>
+        <v>0.1484943634422163</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08861586763380859</v>
+        <v>-0.08861586763382728</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07338356488106894</v>
+        <v>-0.0733835648810674</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3188313285141152</v>
+        <v>0.3188313285141093</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08709497460978176</v>
+        <v>0.08709497460976329</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02522888025074731</v>
+        <v>-0.02522888025075874</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1468660565910625</v>
+        <v>0.1468660565910506</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03007768048538289</v>
+        <v>0.03007768048537423</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1728905534553082</v>
+        <v>0.1728905534553006</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2634572701767905</v>
+        <v>0.2634572701767721</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03494807155677718</v>
+        <v>0.03494807155676655</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0289896731616702</v>
+        <v>0.02898967316165668</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1232164204335809</v>
+        <v>0.1232164204335648</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.09264696680975604</v>
+        <v>-0.09264696680976189</v>
       </c>
       <c r="R12" t="n">
-        <v>0.03436012921367028</v>
+        <v>0.03436012921365714</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1547800711594426</v>
+        <v>0.1547800711594351</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01641478967132813</v>
+        <v>0.01641478967131457</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1198359538187795</v>
+        <v>0.1198359538187636</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1125024674997743</v>
+        <v>-0.1125024674997722</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2391709531182165</v>
+        <v>0.2391709531182024</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2005518668039281</v>
+        <v>0.2005518668039172</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1587028810529416</v>
+        <v>0.1587028810529293</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0330016386356885</v>
+        <v>0.0330016386356788</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1065689050234612</v>
+        <v>0.1065689050234527</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2741631124788561</v>
+        <v>0.2741631124788452</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1992602346257554</v>
+        <v>-0.1992602346257747</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1959727477998743</v>
+        <v>-0.1959727477998873</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1981647913917164</v>
+        <v>-0.1981647913917191</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1907705700167405</v>
+        <v>-0.1907705700167528</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2039339315706516</v>
+        <v>-0.2039339315706644</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1922286209241691</v>
+        <v>-0.1922286209241904</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1976792979072542</v>
+        <v>-0.1976792979072694</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1961814045468532</v>
+        <v>-0.1961814045468581</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1965485744034622</v>
+        <v>-0.1965485744034797</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2006421072058485</v>
+        <v>-0.2006421072058502</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1956657528153144</v>
+        <v>-0.1956657528153134</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2722507502360495</v>
+        <v>-0.2722507502360534</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1922272390144621</v>
+        <v>-0.1922272390144736</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1999976458404201</v>
+        <v>-0.1999976458404377</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1852459636898911</v>
+        <v>-0.1852459636898929</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.1993908504599858</v>
+        <v>-0.1993908504599952</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.1922286209241805</v>
+        <v>-0.1922286209242018</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.1848835124424607</v>
+        <v>-0.184883512442465</v>
       </c>
     </row>
     <row r="14">
@@ -6085,7 +6085,7 @@
         <v>-0.8720086263092969</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9038587063435789</v>
+        <v>-0.9038587063435787</v>
       </c>
       <c r="H14" t="n">
         <v>-0.8720086263092969</v>
@@ -6109,10 +6109,10 @@
         <v>-0.8720086263092969</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9038587063435789</v>
+        <v>-0.9038587063435787</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9038587063435789</v>
+        <v>-0.9038587063435787</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.8720086263092969</v>
@@ -6127,16 +6127,16 @@
         <v>-0.8720086263092969</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9038587063435789</v>
+        <v>-0.9038587063435787</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9016999701260371</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.9038587063435789</v>
+        <v>-0.9038587063435787</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9038587063435789</v>
+        <v>-0.9038587063435787</v>
       </c>
       <c r="Y14" t="n">
         <v>-0.8720086263092969</v>
@@ -6161,82 +6161,82 @@
         <v>-0.6797755560620391</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.7808891821910653</v>
+        <v>-0.7808891821910652</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5475335013432807</v>
+        <v>-0.5475335013432809</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7846437324193203</v>
+        <v>-0.7846437324193201</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7694114296665685</v>
+        <v>-0.7694114296665686</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4090466163056737</v>
+        <v>-0.4090466163056748</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6089328901757288</v>
+        <v>-0.6089328901757284</v>
       </c>
       <c r="I15" t="n">
         <v>-0.7212567450362573</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5679539199899968</v>
+        <v>-0.5679539199899978</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6659501843001289</v>
+        <v>-0.6659501843001291</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5231373113302015</v>
+        <v>-0.5231373113302026</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4325705946087211</v>
+        <v>-0.432570594608721</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6610797932287329</v>
+        <v>-0.6610797932287331</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6988882716581242</v>
+        <v>-0.6988882716581233</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6046615243862155</v>
+        <v>-0.6046615243862148</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.7886748315952612</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.661667735571842</v>
+        <v>-0.6616677355718422</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5412477936260693</v>
+        <v>-0.5412477936260698</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6796130751141831</v>
+        <v>-0.6796130751141833</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6080419910010115</v>
+        <v>-0.6080419910010119</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7601270125772154</v>
+        <v>-0.7601270125772156</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4887069917015776</v>
+        <v>-0.4887069917015772</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5273260780158637</v>
+        <v>-0.5273260780158636</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.5373249837325673</v>
+        <v>-0.5373249837325672</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.6630262261498225</v>
+        <v>-0.6630262261498228</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.5894589597620468</v>
+        <v>-0.5894589597620474</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.4218647523066539</v>
+        <v>-0.4218647523066537</v>
       </c>
     </row>
     <row r="16">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8952880994112655</v>
+        <v>-0.8952880994112654</v>
       </c>
       <c r="C16" t="n">
         <v>-0.8882564857096881</v>
@@ -6255,13 +6255,13 @@
         <v>-0.8882564857096881</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8920006125853875</v>
+        <v>-0.8920006125853874</v>
       </c>
       <c r="F16" t="n">
         <v>-0.8941926561772217</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9186485148365319</v>
+        <v>-0.9186485148365318</v>
       </c>
       <c r="H16" t="n">
         <v>-0.8882564857096881</v>
@@ -6270,7 +6270,7 @@
         <v>-0.8882564857096881</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9187539081517238</v>
+        <v>-0.9187539081517236</v>
       </c>
       <c r="K16" t="n">
         <v>-0.8882564857096881</v>
@@ -6279,16 +6279,16 @@
         <v>-0.8882564857096881</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.888256485709677</v>
+        <v>-0.8882564857096769</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8937071626927623</v>
+        <v>-0.8937071626927622</v>
       </c>
       <c r="O16" t="n">
         <v>-0.9240593493666434</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9244265192232511</v>
+        <v>-0.924426519223251</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.8966699719913545</v>
@@ -6309,22 +6309,22 @@
         <v>-0.9198752953134908</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9201051838342509</v>
+        <v>-0.9201051838342508</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9278755906602174</v>
+        <v>-0.9278755906602173</v>
       </c>
       <c r="Y16" t="n">
         <v>-0.8812738284753958</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.8954187152454859</v>
+        <v>-0.8954187152454858</v>
       </c>
       <c r="AA16" t="n">
         <v>-0.8882564857096881</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.8809113772279686</v>
+        <v>-0.8809113772279688</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5653614416893595</v>
+        <v>-0.5653614416893592</v>
       </c>
       <c r="C2" t="n">
         <v>-0.6750491991129246</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4617567522101055</v>
+        <v>-0.4617567522101087</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7853659769683177</v>
+        <v>-0.7853659769683172</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6503971735060096</v>
+        <v>-0.6503971735060105</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.08543633399673387</v>
+        <v>-0.08543633399673795</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4408334790478995</v>
+        <v>-0.4408334790478991</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6032580549920866</v>
+        <v>-0.6032580549920875</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.316640044870918</v>
+        <v>-0.3166400448709202</v>
       </c>
       <c r="K2" t="n">
         <v>-0.4188728879463034</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3280451504700271</v>
+        <v>-0.3280451504700296</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.177845076829226</v>
+        <v>-0.1778450768292274</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5400245464961621</v>
+        <v>-0.5400245464961629</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5867843821868034</v>
+        <v>-0.5867843821868045</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3504005197819133</v>
+        <v>-0.3504005197819139</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.662779667359352</v>
+        <v>-0.6627796673593532</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5330302708755387</v>
+        <v>-0.5330302708755404</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3241666855104223</v>
+        <v>-0.3241666855104232</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5463837809204488</v>
+        <v>-0.5463837809204498</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2794995010494956</v>
+        <v>-0.2794995010494977</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.4410235748227279</v>
+        <v>-0.4410235748227286</v>
       </c>
       <c r="W2" t="n">
         <v>-0.08329191312750527</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1376830830219642</v>
+        <v>-0.1376830830219657</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01177984705735812</v>
+        <v>0.01177984705735471</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5404256444942568</v>
+        <v>-0.5404256444942571</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3248171390608581</v>
+        <v>-0.3248171390608596</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.116866249225719</v>
+        <v>-0.1168662492257203</v>
       </c>
     </row>
     <row r="3">
@@ -6578,82 +6578,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9270750626810043</v>
+        <v>-0.9270750626810067</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9152290425030046</v>
+        <v>-0.9152290425030047</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9234789542903106</v>
+        <v>-0.9234789542903107</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9263591350192467</v>
+        <v>-0.9263591350192468</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9117481507800991</v>
+        <v>-0.9117481507800975</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9151658356548469</v>
+        <v>-0.9151658356548465</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9145400195455997</v>
+        <v>-0.9145400195455998</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9242209007178126</v>
+        <v>-0.9242209007178149</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9215166620190389</v>
+        <v>-0.9215166620190396</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9221795362673655</v>
+        <v>-0.9221795362673652</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9295698419533274</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.920611109116061</v>
+        <v>-0.9206111091160606</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9198068107980898</v>
+        <v>-0.9198068107980909</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9143779646087393</v>
+        <v>-0.9143779646087397</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9284063563468709</v>
+        <v>-0.9284063563468723</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9018176663067596</v>
+        <v>-0.9018176663067587</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9273108714528441</v>
+        <v>-0.927310871452843</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9143804594560035</v>
+        <v>-0.9143804594560041</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.900188966489484</v>
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02982730163532594</v>
+        <v>0.02982730163534152</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.01069188241782185</v>
+        <v>-0.01069188241781116</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06758999436282778</v>
+        <v>0.06758999436282705</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05184822562187571</v>
+        <v>-0.05184822562186418</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.001969076663013327</v>
+        <v>-0.001969076663006528</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2047543678241449</v>
+        <v>0.2047543678241466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0752162817369733</v>
+        <v>0.07521628173697989</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01601443109098176</v>
+        <v>0.01601443109098875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1093801687358536</v>
+        <v>0.1093801687358625</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08322065931922284</v>
+        <v>0.08322065931922881</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1163263030761866</v>
+        <v>0.1163263030761885</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1709710638693439</v>
+        <v>0.1709710638693502</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03906230241240197</v>
+        <v>0.03906230241240412</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02201889138487488</v>
+        <v>0.02201889138487281</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1081780334720024</v>
+        <v>0.1081780334720025</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.005680497678826642</v>
+        <v>-0.005680497678824271</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04161163374518735</v>
+        <v>0.04161163374519407</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1177399580107256</v>
+        <v>0.1177399580107265</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03674443613864771</v>
+        <v>0.03674443613865026</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1340206222381743</v>
+        <v>0.1340206222381754</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003180302920573932</v>
+        <v>0.003180302920572811</v>
       </c>
       <c r="W4" t="n">
-        <v>0.205535984049918</v>
+        <v>0.2055359840499273</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1857110413167507</v>
+        <v>0.1857110413167506</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2401885242483274</v>
+        <v>0.2401885242483293</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03891610690202611</v>
+        <v>0.0389161069020252</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1175028753296028</v>
+        <v>0.1175028753296159</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.193890142365231</v>
+        <v>0.1938901423652267</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1020130657603468</v>
+        <v>-0.1020130657603457</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.09823461499939221</v>
+        <v>-0.09823461499938516</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1021887840512805</v>
+        <v>-0.1021887840512707</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1025539711256299</v>
+        <v>-0.1025539711256186</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.09642658635015278</v>
+        <v>-0.09642658635014324</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1087754537602114</v>
+        <v>-0.1087754537602082</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09754559204200373</v>
+        <v>-0.09754559204199265</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1009727572400239</v>
+        <v>-0.1009727572400167</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.09998709398909601</v>
+        <v>-0.09998709398909031</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1002287038687489</v>
+        <v>-0.1002287038687468</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1029223835099313</v>
+        <v>-0.102922383509917</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09965703058949965</v>
+        <v>-0.0996570305894869</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1713305644358388</v>
+        <v>-0.1713305644358382</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.09738512260986013</v>
+        <v>-0.0973851226098475</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.102498306668716</v>
+        <v>-0.1024983066687121</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.09280704136925742</v>
+        <v>-0.09280704136924518</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1020990152886759</v>
+        <v>-0.1020990152886789</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.09738603195239223</v>
+        <v>-0.09738603195238632</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.09162178983766478</v>
+        <v>-0.09162178983766747</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7709153249715611</v>
+        <v>-0.7709153249715616</v>
       </c>
       <c r="C6" t="n">
         <v>-0.8114345090247084</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7331526322440595</v>
+        <v>-0.733152632244062</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8525908522287616</v>
+        <v>-0.8525908522287614</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8027117032698984</v>
+        <v>-0.8027117032698986</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6330046959108662</v>
+        <v>-0.6330046959108687</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7255263448699135</v>
+        <v>-0.725526344869914</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7847281955159046</v>
+        <v>-0.784728195515906</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7162026359591092</v>
+        <v>-0.7162026359591085</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7175219672876632</v>
+        <v>-0.7175219672876622</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6844163235307011</v>
+        <v>-0.6844163235307031</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6297715627375435</v>
+        <v>-0.629771562737544</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7616803241944849</v>
+        <v>-0.7616803241944866</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8157401723501356</v>
+        <v>-0.8157401723501375</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7295810302630079</v>
+        <v>-0.7295810302630109</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8064231242857125</v>
+        <v>-0.8064231242857144</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.759130992861699</v>
+        <v>-0.7591309928617005</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6830026685961603</v>
+        <v>-0.683002668596162</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7639981904682376</v>
+        <v>-0.7639981904682389</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7037384414968375</v>
+        <v>-0.7037384414968395</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7613220895096205</v>
+        <v>-0.7613220895096214</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6322230796850936</v>
+        <v>-0.6322230796850908</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6520480224182594</v>
+        <v>-0.6520480224182617</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.5605541023585575</v>
+        <v>-0.5605541023585603</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7618265197048603</v>
+        <v>-0.7618265197048616</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.6832397512772824</v>
+        <v>-0.6832397512772818</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.6068524842416531</v>
+        <v>-0.6068524842416535</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.902755692367233</v>
+        <v>-0.9027556923672325</v>
       </c>
       <c r="C7" t="n">
         <v>-0.8989772416062786</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.902931410658167</v>
+        <v>-0.9029314106581671</v>
       </c>
       <c r="F7" t="n">
         <v>-0.9032965977325151</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.934185650085164</v>
+        <v>-0.9341856500851642</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9343582584551744</v>
+        <v>-0.9343582584551741</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8982882186488889</v>
+        <v>-0.898288218648889</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9017153838469119</v>
+        <v>-0.9017153838469149</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9377461577241073</v>
+        <v>-0.937746157724109</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9379877676037598</v>
+        <v>-0.937987767603761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9036650101168177</v>
+        <v>-0.9036650101168183</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.937416094324511</v>
+        <v>-0.9374160943245119</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9358329568660322</v>
+        <v>-0.9358329568660319</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9351441863448701</v>
+        <v>-0.9351441863448691</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9402573704037265</v>
+        <v>-0.9402573704037297</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8935496679761435</v>
+        <v>-0.8935496679761439</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9028416418955624</v>
+        <v>-0.9028416418955652</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.8981286585592776</v>
+        <v>-0.8981286585592765</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.8923644164445502</v>
+        <v>-0.8923644164445503</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8700191923443538</v>
+        <v>-0.8700191923443537</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.8733062377054966</v>
+        <v>-0.8733062377054969</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5286781857989549</v>
+        <v>-0.5286781857989539</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.6456479719138482</v>
+        <v>-0.6456479719138485</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4173339162535051</v>
+        <v>-0.4173339162535065</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7626039947807305</v>
+        <v>-0.7626039947807303</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6187103418849665</v>
+        <v>-0.6187103418849687</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.01290123765939402</v>
+        <v>-0.01290123765939745</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3948476120287129</v>
+        <v>-0.3948476120287132</v>
       </c>
       <c r="I9" t="n">
         <v>-0.5694057894204432</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2605325108503824</v>
+        <v>-0.2605325108503836</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3712464991130363</v>
+        <v>-0.3712464991130365</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2736336580863064</v>
+        <v>-0.2736336580863061</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1120417101640324</v>
+        <v>-0.1120417101640332</v>
       </c>
       <c r="N9" t="n">
         <v>-0.5014485487814039</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5517014840028567</v>
+        <v>-0.5517014840028576</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2976590403249123</v>
+        <v>-0.2976590403249121</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.6333738441920159</v>
+        <v>-0.6333738441920156</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.4939317798601117</v>
+        <v>-0.493931779860112</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2694654601982108</v>
+        <v>-0.2694654601982115</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5082828370303187</v>
+        <v>-0.5082828370303184</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2214615035100349</v>
+        <v>-0.221461503510037</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3929900042759381</v>
+        <v>-0.3929900042759387</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0105966221397463</v>
+        <v>-0.01059662213974719</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.06905097504655684</v>
+        <v>-0.06905097504655749</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09157728278087546</v>
+        <v>0.09157728278087292</v>
       </c>
       <c r="Z9" t="n">
         <v>-0.5018796099991772</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.2701645045736179</v>
+        <v>-0.2701645045736175</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.04767952231228429</v>
+        <v>-0.0476795223122863</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.9174128957467976</v>
+        <v>-0.9174128957467979</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9110344244452472</v>
+        <v>-0.9110344244452471</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9152874870070853</v>
+        <v>-0.9152874870070854</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9009410177017845</v>
+        <v>-0.9009410177017846</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9037699677059522</v>
+        <v>-0.9037699677059524</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9143455193514503</v>
+        <v>-0.9143455193514504</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9114392659366201</v>
+        <v>-0.9114392659366202</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9121516588731887</v>
+        <v>-0.9121516588731889</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.92009404248977</v>
+        <v>-0.9200940424897701</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9104660655243257</v>
+        <v>-0.9104660655243259</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9075397794669351</v>
+        <v>-0.9075397794669352</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9037672864861631</v>
+        <v>-0.9037672864861632</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.918843641029868</v>
+        <v>-0.9188436410298682</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.8902686963476646</v>
+        <v>-0.8902686963476647</v>
       </c>
       <c r="Z10" t="n">
         <v>-0.9176663201389261</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.9037699677059771</v>
+        <v>-0.9037699677059772</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.889518788570161</v>
+        <v>-0.8895187885701611</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1954032953869684</v>
+        <v>-0.1954032953869654</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574734</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1846694824608857</v>
+        <v>-0.1846694824608777</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2471189086682289</v>
+        <v>-0.2471189086682263</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.1862851488574832</v>
+        <v>-0.1862851488574743</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.01689169619269453</v>
+        <v>-0.0168916961926925</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.07438532103794301</v>
+        <v>-0.07438532103793499</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03783684418119616</v>
+        <v>0.0378368441812077</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1318721808967432</v>
+        <v>-0.1318721808967333</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.06114479075622094</v>
+        <v>-0.06114479075621017</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2366257919134699</v>
+        <v>0.2366257919134785</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0488894346166991</v>
+        <v>0.04888943461670918</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03691034922468296</v>
+        <v>-0.03691034922468231</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1057905764409855</v>
+        <v>0.1057905764409895</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06048998187743695</v>
+        <v>0.06048998187744886</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1084691758938915</v>
+        <v>0.1084691758939002</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1878957281723622</v>
+        <v>0.1878957281723711</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.003507637049239294</v>
+        <v>-0.003507637049227537</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.02820823282665206</v>
+        <v>-0.02820823282664425</v>
       </c>
       <c r="P12" t="n">
-        <v>0.09666008947021264</v>
+        <v>0.09666008947022128</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.06835227508667098</v>
+        <v>-0.06835227508666203</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0001870460545229657</v>
+        <v>0.0001870460545195934</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1105179511684193</v>
+        <v>0.1105179511684284</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.00686686354454117</v>
+        <v>-0.006866863544531856</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1341131167969735</v>
+        <v>0.1341131167969842</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0110312637377875</v>
+        <v>-0.01103126373779247</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2377585690561844</v>
+        <v>0.2377585690561808</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2090267678943461</v>
+        <v>0.2090267678943552</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2879796419810359</v>
+        <v>0.2879796419810415</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.003719514601237094</v>
+        <v>-0.003719514601225443</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1101743530786504</v>
+        <v>0.1101743530786633</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2195313804675051</v>
+        <v>0.2195313804675144</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2079646930785275</v>
+        <v>-0.2079646930785248</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2048295122059457</v>
+        <v>-0.2048295122059394</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2069200006260373</v>
+        <v>-0.2069200006260342</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.199868346079258</v>
+        <v>-0.19986834607925</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2103769934863588</v>
+        <v>-0.2103769934863554</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2012588469568596</v>
+        <v>-0.2012588469568556</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2064569995656063</v>
+        <v>-0.2064569995656079</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2050285020955566</v>
+        <v>-0.205028502095555</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2053786613426403</v>
+        <v>-0.205378661342632</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2092825448940747</v>
+        <v>-0.2092825448940665</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2045501493408654</v>
+        <v>-0.2045501493408599</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2639455651282361</v>
+        <v>-0.2639455651282368</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2012575290691397</v>
+        <v>-0.2012575290691358</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.208667940774248</v>
+        <v>-0.2086679407742449</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1946226286975133</v>
+        <v>-0.1946226286975065</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.2080892576127694</v>
+        <v>-0.2080892576127661</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.2012588469568719</v>
+        <v>-0.2012588469568678</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.1942540299519724</v>
+        <v>-0.1942540299519591</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9066512114251848</v>
+        <v>-0.9066512114251849</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9052993081818289</v>
+        <v>-0.905299308181829</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659563</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9066512114251848</v>
+        <v>-0.9066512114251849</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9066512114251848</v>
+        <v>-0.9066512114251849</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="S14" t="n">
         <v>-0.8732061250693598</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="U14" t="n">
         <v>-0.9066512114251849</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9044935669580234</v>
+        <v>-0.9044935669580235</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.9066512114251848</v>
+        <v>-0.9066512114251849</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9066512114251848</v>
+        <v>-0.9066512114251849</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.8748217914659558</v>
+        <v>-0.8748217914659562</v>
       </c>
     </row>
     <row r="15">
@@ -7634,76 +7634,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.7054283388011691</v>
+        <v>-0.7054283388011685</v>
       </c>
       <c r="C15" t="n">
         <v>-0.7629219636464171</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6506997984272775</v>
+        <v>-0.6506997984272783</v>
       </c>
       <c r="E15" t="n">
         <v>-0.820408823505218</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7496814333646967</v>
+        <v>-0.7496814333646974</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4837402706542356</v>
+        <v>-0.4837402706542371</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6396472079917749</v>
+        <v>-0.6396472079917751</v>
       </c>
       <c r="I15" t="n">
         <v>-0.7254469918331565</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6041054363538746</v>
+        <v>-0.6041054363538749</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.628046660731037</v>
+        <v>-0.6280466607310371</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5800674667145834</v>
+        <v>-0.5800674667145835</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5006409144361115</v>
+        <v>-0.5006409144361126</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6920442796577112</v>
+        <v>-0.6920442796577113</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7485742953943557</v>
+        <v>-0.7485742953943562</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6237059730974923</v>
+        <v>-0.6237059730974931</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.756888917695144</v>
+        <v>-0.7568889176951443</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.6883495965539506</v>
+        <v>-0.6883495965539503</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5780186914400541</v>
+        <v>-0.5780186914400545</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6954035061530163</v>
+        <v>-0.6954035061530162</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5862529457707294</v>
+        <v>-0.5862529457707295</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6684059220275893</v>
+        <v>-0.6684059220275897</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4826074935115194</v>
+        <v>-0.4826074935115207</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5113392946733579</v>
+        <v>-0.511339294673358</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.4005570006274398</v>
+        <v>-0.4005570006274418</v>
       </c>
       <c r="Z15" t="n">
         <v>-0.6922561572097111</v>
@@ -7712,7 +7712,7 @@
         <v>-0.5783622895298242</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.4690052621409702</v>
+        <v>-0.4690052621409704</v>
       </c>
     </row>
     <row r="16">
@@ -7725,82 +7725,82 @@
         <v>-0.8965013356870026</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="E16" t="n">
         <v>-0.8933661548144198</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8954566432345106</v>
+        <v>-0.8954566432345109</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9202344086469608</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9202730062812183</v>
+        <v>-0.9202730062812184</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8897954895653333</v>
+        <v>-0.8897954895653334</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8949936421740808</v>
+        <v>-0.894993642174081</v>
       </c>
       <c r="O16" t="n">
         <v>-0.9253945646632595</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9257447239103428</v>
+        <v>-0.9257447239103429</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.8978191875025485</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9249162119085682</v>
+        <v>-0.9249162119085683</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9213202234180344</v>
+        <v>-0.9213202234180345</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9216235916368423</v>
+        <v>-0.9216235916368424</v>
       </c>
       <c r="X16" t="n">
         <v>-0.92903400334195</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.8831592713059885</v>
+        <v>-0.8831592713059886</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.8966259002212437</v>
+        <v>-0.8966259002212438</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.8897954895653454</v>
+        <v>-0.8897954895653455</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.8827906725604461</v>
+        <v>-0.8827906725604462</v>
       </c>
     </row>
   </sheetData>
@@ -9469,7 +9469,7 @@
         <v>-0.8832601170827331</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9739955348316283</v>
+        <v>-0.9739955348316282</v>
       </c>
       <c r="L2" t="n">
         <v>-1.265267448595558</v>
@@ -9505,7 +9505,7 @@
         <v>-0.8812727213642814</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5158949918552035</v>
+        <v>-0.5158949918552037</v>
       </c>
       <c r="X2" t="n">
         <v>-0.1835892271588484</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2322366762852253</v>
+        <v>-0.2322366762852255</v>
       </c>
       <c r="C4" t="n">
         <v>-0.1525968403762313</v>
@@ -9678,10 +9678,10 @@
         <v>-0.1555165013207375</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2051210250147008</v>
+        <v>-0.2051210250147007</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.01086405789449415</v>
+        <v>-0.01086405789449403</v>
       </c>
       <c r="X4" t="n">
         <v>0.1102574912060224</v>
@@ -9763,7 +9763,7 @@
         <v>-0.1645748098033992</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1660272655605634</v>
+        <v>-0.1660272655605635</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2266510695060844</v>
@@ -9775,10 +9775,10 @@
         <v>-0.1677916097358675</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1617337254566142</v>
+        <v>-0.161733725456614</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1675403633628392</v>
+        <v>-0.1675403633628391</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.1645748098033992</v>
@@ -9930,7 +9930,7 @@
         <v>-0.9173385355824584</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.913854893503167</v>
+        <v>-0.9138548935031668</v>
       </c>
       <c r="S7" t="n">
         <v>-0.9138548935031668</v>
@@ -10082,7 +10082,7 @@
         <v>-0.9518400173021848</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8686387201593938</v>
+        <v>-0.8686387201593937</v>
       </c>
       <c r="K9" t="n">
         <v>-0.9663654073010982</v>
@@ -10325,7 +10325,7 @@
         <v>-0.3606110073206468</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2456217797805381</v>
+        <v>-0.2456217797805382</v>
       </c>
       <c r="D12" t="n">
         <v>-0.2405550689209001</v>
@@ -10364,7 +10364,7 @@
         <v>-0.2706939771746021</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3593762863187667</v>
+        <v>-0.3593762863187666</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.2599729376335895</v>
@@ -10382,13 +10382,13 @@
         <v>-0.2494223475676352</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.284825701072514</v>
+        <v>-0.2848257010725139</v>
       </c>
       <c r="W12" t="n">
         <v>-0.03978112448638557</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1357573530774328</v>
+        <v>0.1357573530774326</v>
       </c>
       <c r="Y12" t="n">
         <v>-0.1445880590473999</v>
@@ -10397,10 +10397,10 @@
         <v>-0.2532792356291804</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.03644837874525029</v>
+        <v>0.03644837874525018</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2702190513788646</v>
+        <v>-0.2702190513788645</v>
       </c>
     </row>
     <row r="13">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2667698548224853</v>
+        <v>-0.2667698548224852</v>
       </c>
       <c r="C13" t="n">
         <v>-0.2625503309211982</v>
@@ -10476,13 +10476,13 @@
         <v>-0.2625495016631039</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2672123598249458</v>
+        <v>-0.2672123598249457</v>
       </c>
       <c r="Y13" t="n">
         <v>-0.2584328173609139</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.2668482346453849</v>
+        <v>-0.2668482346453848</v>
       </c>
       <c r="AA13" t="n">
         <v>-0.2625503309211982</v>
